--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>73379.10000000001</v>
+        <v>71502.32000000001</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>7446.4</v>
+        <v>7274.71</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>65094.36</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>14794.17</v>
+        <v>14614.26</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>70420.27</v>
+        <v>69563.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1255.55</v>
+        <v>1239.87</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>10987.16</v>
+        <v>10849.94</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1725.99</v>
+        <v>1723.24</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5917.67</v>
+        <v>5919.55</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>70017.3</v>
+        <v>70039.59</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>46749.59</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7939.54</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>66869.66</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>22292.41</v>
+        <v>22149.61</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>51483.72</v>
+        <v>51153.93</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>72787.33</v>
+        <v>72321.07000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>44446.44</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>51187.84</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>66573.78</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>72195.57000000001</v>
+        <v>72653.84</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10898.37</v>
+        <v>10967.55</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>40240.15</v>
+        <v>40771.06</v>
       </c>
     </row>
     <row r="24">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10405.24</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>51150.89</v>
+        <v>51905.57</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9418.959999999999</v>
+        <v>9557.92</v>
       </c>
     </row>
     <row r="27">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>9369.639999999999</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4586.19</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>77521.47</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>36837.49</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7051.89</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>60310.91</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>7002.58</v>
+        <v>7205.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Superintendencia de Salud</t>
+          <t>SUPERINTENDENCIA DE SALUD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar de los T.T.A.</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar</t>
+          <t>SUBSECRETARIA DE CIENCIA, TECNOLOGIA, CONOCIMIENTO E INNOVACION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Servicio del Bienestar Gobierno Regional Coquimbo</t>
+          <t>GOBIERNO REGIONAL IV REGION COQUIMBO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1277,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1342,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1407,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1472,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1537,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1602,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1668,7 +1732,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1729,7 +1797,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1790,7 +1862,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1851,7 +1927,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1912,7 +1992,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1973,7 +2057,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2034,7 +2122,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2095,7 +2187,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2156,7 +2252,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2217,7 +2317,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2278,7 +2382,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2339,7 +2447,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2400,7 +2512,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2461,7 +2577,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
